--- a/output_phyto/phyto_Intermediate_badger_2019.xlsx
+++ b/output_phyto/phyto_Intermediate_badger_2019.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="326">
   <si>
     <t>NA</t>
   </si>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">10.5194/cp-15-539-2019</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_badger_2019.xlsx</t>
+    <t xml:space="preserve">phytoplankton_badger_2019_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">Mk37_2</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Dcell = 0.55 + 0.88*Lcocco (Henderiks and Pagani, 2007)</t>
@@ -1485,9 +1485,6 @@
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Badger_2019_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alkenone unsaturation; uncertainty from analytical and calibration error</t>
   </si>
   <si>
     <t xml:space="preserve">phytoplankton_Badger_2019_3</t>
@@ -1630,7 +1627,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1696,12 +1693,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1815,7 +1806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1914,7 +1905,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2640,7 +2630,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2658,8 +2648,8 @@
       <c r="H5" t="n">
         <v>0.111324356079102</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2677,7 +2667,7 @@
         <v>-23.5746666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2689,7 +2679,7 @@
         <v>26.6034549663469</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2707,10 +2697,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA5" t="e">
         <v>#N/A</v>
@@ -2728,7 +2718,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.27908</v>
+        <v>1.27530541703466</v>
       </c>
       <c r="AG5" t="s">
         <v>278</v>
@@ -2750,7 +2740,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2768,8 +2758,8 @@
       <c r="H6" t="n">
         <v>0.119055961608887</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2787,7 +2777,7 @@
         <v>-24.4173333333333</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2799,7 +2789,7 @@
         <v>26.5862336817011</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2808,7 +2798,7 @@
         <v>#N/A</v>
       </c>
       <c r="V6" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W6" t="n">
         <v>0.2</v>
@@ -2817,10 +2807,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA6" t="e">
         <v>#N/A</v>
@@ -2838,7 +2828,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.32396</v>
+        <v>1.32010981771309</v>
       </c>
       <c r="AG6" t="s">
         <v>278</v>
@@ -2855,12 +2845,12 @@
     </row>
     <row r="7" ht="19" customHeight="1">
       <c r="A7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2878,8 +2868,8 @@
       <c r="H7" t="n">
         <v>0.123774566650391</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2897,7 +2887,7 @@
         <v>-23.8245</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2909,7 +2899,7 @@
         <v>27.8683058850899</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2918,7 +2908,7 @@
         <v>#N/A</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W7" t="n">
         <v>0.2</v>
@@ -2927,10 +2917,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA7" t="e">
         <v>#N/A</v>
@@ -2948,7 +2938,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.26808</v>
+        <v>1.26432394628014</v>
       </c>
       <c r="AG7" t="s">
         <v>278</v>
@@ -2965,12 +2955,12 @@
     </row>
     <row r="8" ht="19" customHeight="1">
       <c r="A8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2988,8 +2978,8 @@
       <c r="H8" t="n">
         <v>0.127484924316406</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -3007,7 +2997,7 @@
         <v>-24.2376666666667</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -3019,7 +3009,7 @@
         <v>28.2099957112115</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -3028,7 +3018,7 @@
         <v>#N/A</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W8" t="n">
         <v>0.2</v>
@@ -3037,10 +3027,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA8" t="e">
         <v>#N/A</v>
@@ -3058,7 +3048,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.29888</v>
+        <v>1.29507206439279</v>
       </c>
       <c r="AG8" t="s">
         <v>278</v>
@@ -3075,12 +3065,12 @@
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -3098,8 +3088,8 @@
       <c r="H9" t="n">
         <v>0.131907974243164</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -3117,7 +3107,7 @@
         <v>-23.754</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3129,7 +3119,7 @@
         <v>26.953348195855</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3138,7 +3128,7 @@
         <v>#N/A</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W9" t="n">
         <v>0.2</v>
@@ -3147,10 +3137,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA9" t="e">
         <v>#N/A</v>
@@ -3168,7 +3158,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.21396</v>
+        <v>1.21029511016791</v>
       </c>
       <c r="AG9" t="s">
         <v>278</v>
@@ -3185,12 +3175,12 @@
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3206,10 +3196,10 @@
         <v>-78.7393333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>0.133215209960938</v>
-      </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+        <v>0.133215209960937</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3227,7 +3217,7 @@
         <v>-24.5236666666667</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3239,7 +3229,7 @@
         <v>28.3656204847738</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3248,7 +3238,7 @@
         <v>#N/A</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W10" t="n">
         <v>0.2</v>
@@ -3257,10 +3247,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA10" t="e">
         <v>#N/A</v>
@@ -3278,7 +3268,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.31824</v>
+        <v>1.31439945292074</v>
       </c>
       <c r="AG10" t="s">
         <v>278</v>
@@ -3295,12 +3285,12 @@
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3318,8 +3308,8 @@
       <c r="H11" t="n">
         <v>0.135568237304688</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3337,7 +3327,7 @@
         <v>-23.8086666666667</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3349,7 +3339,7 @@
         <v>25.7871677256865</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3358,7 +3348,7 @@
         <v>#N/A</v>
       </c>
       <c r="V11" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W11" t="n">
         <v>0.2</v>
@@ -3367,10 +3357,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA11" t="e">
         <v>#N/A</v>
@@ -3388,7 +3378,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.309</v>
+        <v>1.30517501748695</v>
       </c>
       <c r="AG11" t="s">
         <v>278</v>
@@ -3405,12 +3395,12 @@
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
         <v>271</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" t="s">
         <v>272</v>
       </c>
       <c r="D12" t="s">
@@ -3428,8 +3418,8 @@
       <c r="H12" t="n">
         <v>0.138967041015625</v>
       </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3447,7 +3437,7 @@
         <v>-23.792</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P12" t="e">
         <v>#N/A</v>
@@ -3459,7 +3449,7 @@
         <v>26.5561278454044</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="e">
         <v>#N/A</v>
@@ -3468,7 +3458,7 @@
         <v>#N/A</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W12" t="n">
         <v>0.2</v>
@@ -3477,10 +3467,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA12" t="e">
         <v>#N/A</v>
@@ -3498,7 +3488,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.27556</v>
+        <v>1.27179134639321</v>
       </c>
       <c r="AG12" t="s">
         <v>278</v>
@@ -3515,12 +3505,12 @@
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
         <v>271</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" t="s">
         <v>272</v>
       </c>
       <c r="D13" t="s">
@@ -3538,8 +3528,8 @@
       <c r="H13" t="n">
         <v>0.146694732666016</v>
       </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3557,7 +3547,7 @@
         <v>-23.2865</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P13" t="e">
         <v>#N/A</v>
@@ -3569,7 +3559,7 @@
         <v>26.0275691372576</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T13" t="e">
         <v>#N/A</v>
@@ -3578,7 +3568,7 @@
         <v>#N/A</v>
       </c>
       <c r="V13" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W13" t="n">
         <v>0.2</v>
@@ -3587,10 +3577,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA13" t="e">
         <v>#N/A</v>
@@ -3608,7 +3598,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.20472</v>
+        <v>1.20107067473411</v>
       </c>
       <c r="AG13" t="s">
         <v>278</v>
@@ -3625,12 +3615,12 @@
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B14" t="s">
         <v>271</v>
       </c>
-      <c r="C14" s="34" t="s">
+      <c r="C14" t="s">
         <v>272</v>
       </c>
       <c r="D14" t="s">
@@ -3648,8 +3638,8 @@
       <c r="H14" t="n">
         <v>0.150037734985352</v>
       </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3667,7 +3657,7 @@
         <v>-23.8325</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P14" t="e">
         <v>#N/A</v>
@@ -3679,7 +3669,7 @@
         <v>25.7261215752229</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="e">
         <v>#N/A</v>
@@ -3688,7 +3678,7 @@
         <v>#N/A</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W14" t="n">
         <v>0.2</v>
@@ -3697,10 +3687,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA14" t="e">
         <v>#N/A</v>
@@ -3718,7 +3708,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.27688</v>
+        <v>1.27310912288375</v>
       </c>
       <c r="AG14" t="s">
         <v>278</v>
@@ -3735,12 +3725,12 @@
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B15" t="s">
         <v>271</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" t="s">
         <v>272</v>
       </c>
       <c r="D15" t="s">
@@ -3756,10 +3746,10 @@
         <v>-78.7393333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>0.169761596679688</v>
-      </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+        <v>0.169761596679687</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3777,7 +3767,7 @@
         <v>-23.8695</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P15" t="e">
         <v>#N/A</v>
@@ -3789,7 +3779,7 @@
         <v>26.2468831753025</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T15" t="e">
         <v>#N/A</v>
@@ -3798,7 +3788,7 @@
         <v>#N/A</v>
       </c>
       <c r="V15" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W15" t="n">
         <v>0.2</v>
@@ -3807,10 +3797,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA15" t="e">
         <v>#N/A</v>
@@ -3828,7 +3818,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.24256</v>
+        <v>1.23884693412965</v>
       </c>
       <c r="AG15" t="s">
         <v>278</v>
@@ -3845,12 +3835,12 @@
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B16" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="34" t="s">
+      <c r="C16" t="s">
         <v>272</v>
       </c>
       <c r="D16" t="s">
@@ -3868,8 +3858,8 @@
       <c r="H16" t="n">
         <v>0.179935256958008</v>
       </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3887,7 +3877,7 @@
         <v>-23.656</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P16" t="e">
         <v>#N/A</v>
@@ -3899,7 +3889,7 @@
         <v>26.1987024301441</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T16" t="e">
         <v>#N/A</v>
@@ -3908,7 +3898,7 @@
         <v>#N/A</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W16" t="n">
         <v>0.2</v>
@@ -3917,10 +3907,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA16" t="e">
         <v>#N/A</v>
@@ -3938,7 +3928,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.30504</v>
+        <v>1.30122168801532</v>
       </c>
       <c r="AG16" t="s">
         <v>278</v>
@@ -3955,12 +3945,12 @@
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B17" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" t="s">
         <v>272</v>
       </c>
       <c r="D17" t="s">
@@ -3978,8 +3968,8 @@
       <c r="H17" t="n">
         <v>0.184372253417969</v>
       </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3997,7 +3987,7 @@
         <v>-23.6015</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P17" t="e">
         <v>#N/A</v>
@@ -4009,7 +3999,7 @@
         <v>24.0984887000774</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T17" t="e">
         <v>#N/A</v>
@@ -4018,7 +4008,7 @@
         <v>#N/A</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W17" t="n">
         <v>0.2</v>
@@ -4027,10 +4017,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA17" t="e">
         <v>#N/A</v>
@@ -4048,7 +4038,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.38908</v>
+        <v>1.38512012457984</v>
       </c>
       <c r="AG17" t="s">
         <v>278</v>
@@ -4065,12 +4055,12 @@
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
         <v>271</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" t="s">
         <v>272</v>
       </c>
       <c r="D18" t="s">
@@ -4088,8 +4078,8 @@
       <c r="H18" t="n">
         <v>0.190008972167969</v>
       </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -4107,7 +4097,7 @@
         <v>-23.6068</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P18" t="e">
         <v>#N/A</v>
@@ -4119,7 +4109,7 @@
         <v>26.425930594289</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T18" t="e">
         <v>#N/A</v>
@@ -4128,7 +4118,7 @@
         <v>#N/A</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W18" t="n">
         <v>0.2</v>
@@ -4137,10 +4127,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA18" t="e">
         <v>#N/A</v>
@@ -4158,7 +4148,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.33408</v>
+        <v>1.33021277080725</v>
       </c>
       <c r="AG18" t="s">
         <v>278</v>
@@ -4175,12 +4165,12 @@
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B19" t="s">
         <v>271</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" t="s">
         <v>272</v>
       </c>
       <c r="D19" t="s">
@@ -4198,8 +4188,8 @@
       <c r="H19" t="n">
         <v>0.191676605224609</v>
       </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -4217,7 +4207,7 @@
         <v>-23.638</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P19" t="e">
         <v>#N/A</v>
@@ -4229,7 +4219,7 @@
         <v>27.0758431640611</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T19" t="e">
         <v>#N/A</v>
@@ -4238,7 +4228,7 @@
         <v>#N/A</v>
       </c>
       <c r="V19" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W19" t="n">
         <v>0.2</v>
@@ -4247,10 +4237,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA19" t="e">
         <v>#N/A</v>
@@ -4268,7 +4258,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.23464</v>
+        <v>1.2309402751864</v>
       </c>
       <c r="AG19" t="s">
         <v>278</v>
@@ -4285,12 +4275,12 @@
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B20" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="34" t="s">
+      <c r="C20" t="s">
         <v>272</v>
       </c>
       <c r="D20" t="s">
@@ -4308,8 +4298,8 @@
       <c r="H20" t="n">
         <v>0.19806916809082</v>
       </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -4327,7 +4317,7 @@
         <v>-23.6056666666667</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P20" t="e">
         <v>#N/A</v>
@@ -4339,7 +4329,7 @@
         <v>26.8635196163856</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" t="e">
         <v>#N/A</v>
@@ -4348,7 +4338,7 @@
         <v>#N/A</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W20" t="n">
         <v>0.2</v>
@@ -4357,10 +4347,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA20" t="e">
         <v>#N/A</v>
@@ -4378,7 +4368,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.25224</v>
+        <v>1.24851062839363</v>
       </c>
       <c r="AG20" t="s">
         <v>278</v>
@@ -4395,12 +4385,12 @@
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B21" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" t="s">
         <v>272</v>
       </c>
       <c r="D21" t="s">
@@ -4418,8 +4408,8 @@
       <c r="H21" t="n">
         <v>0.211565612792969</v>
       </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -4437,7 +4427,7 @@
         <v>-24.0916666666667</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P21" t="e">
         <v>#N/A</v>
@@ -4449,7 +4439,7 @@
         <v>27.8806560758742</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T21" t="e">
         <v>#N/A</v>
@@ -4458,7 +4448,7 @@
         <v>#N/A</v>
       </c>
       <c r="V21" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W21" t="n">
         <v>0.2</v>
@@ -4467,10 +4457,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA21" t="e">
         <v>#N/A</v>
@@ -4488,7 +4478,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.32968</v>
+        <v>1.32582018250544</v>
       </c>
       <c r="AG21" t="s">
         <v>278</v>
@@ -4505,12 +4495,12 @@
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B22" t="s">
         <v>271</v>
       </c>
-      <c r="C22" s="34" t="s">
+      <c r="C22" t="s">
         <v>272</v>
       </c>
       <c r="D22" t="s">
@@ -4526,10 +4516,10 @@
         <v>-78.7393333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.220435913085938</v>
-      </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+        <v>0.220435913085937</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -4547,7 +4537,7 @@
         <v>-23.935</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P22" t="e">
         <v>#N/A</v>
@@ -4559,7 +4549,7 @@
         <v>26.295888135523</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="e">
         <v>#N/A</v>
@@ -4568,7 +4558,7 @@
         <v>#N/A</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W22" t="n">
         <v>0.2</v>
@@ -4577,10 +4567,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA22" t="e">
         <v>#N/A</v>
@@ -4598,7 +4588,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.30724</v>
+        <v>1.30341798216623</v>
       </c>
       <c r="AG22" t="s">
         <v>278</v>
@@ -4615,12 +4605,12 @@
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B23" t="s">
         <v>271</v>
       </c>
-      <c r="C23" s="34" t="s">
+      <c r="C23" t="s">
         <v>272</v>
       </c>
       <c r="D23" t="s">
@@ -4638,8 +4628,8 @@
       <c r="H23" t="n">
         <v>0.223657653808594</v>
       </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4657,7 +4647,7 @@
         <v>-23.7433333333333</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P23" t="e">
         <v>#N/A</v>
@@ -4666,10 +4656,10 @@
         <v>#N/A</v>
       </c>
       <c r="R23" s="11" t="n">
-        <v>26.3235681898576</v>
+        <v>26.3235681898575</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" t="e">
         <v>#N/A</v>
@@ -4678,7 +4668,7 @@
         <v>#N/A</v>
       </c>
       <c r="V23" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W23" t="n">
         <v>0.2</v>
@@ -4687,10 +4677,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA23" t="e">
         <v>#N/A</v>
@@ -4708,7 +4698,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.342</v>
+        <v>1.3381194297505</v>
       </c>
       <c r="AG23" t="s">
         <v>278</v>
@@ -4725,12 +4715,12 @@
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B24" t="s">
         <v>271</v>
       </c>
-      <c r="C24" s="34" t="s">
+      <c r="C24" t="s">
         <v>272</v>
       </c>
       <c r="D24" t="s">
@@ -4748,8 +4738,8 @@
       <c r="H24" t="n">
         <v>0.227098190307617</v>
       </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4767,7 +4757,7 @@
         <v>-23.705</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P24" t="e">
         <v>#N/A</v>
@@ -4779,7 +4769,7 @@
         <v>26.5511214327482</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T24" t="e">
         <v>#N/A</v>
@@ -4788,7 +4778,7 @@
         <v>#N/A</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W24" t="n">
         <v>0.2</v>
@@ -4797,10 +4787,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA24" t="e">
         <v>#N/A</v>
@@ -4818,7 +4808,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.30988</v>
+        <v>1.30605353514731</v>
       </c>
       <c r="AG24" t="s">
         <v>278</v>
@@ -4835,12 +4825,12 @@
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
         <v>271</v>
       </c>
-      <c r="C25" s="34" t="s">
+      <c r="C25" t="s">
         <v>272</v>
       </c>
       <c r="D25" t="s">
@@ -4858,8 +4848,8 @@
       <c r="H25" t="n">
         <v>0.235762832641602</v>
       </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4877,7 +4867,7 @@
         <v>-24.066</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P25" t="e">
         <v>#N/A</v>
@@ -4889,7 +4879,7 @@
         <v>27.4607859592947</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" t="e">
         <v>#N/A</v>
@@ -4898,7 +4888,7 @@
         <v>#N/A</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W25" t="n">
         <v>0.2</v>
@@ -4907,10 +4897,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA25" t="e">
         <v>#N/A</v>
@@ -4928,7 +4918,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.38116</v>
+        <v>1.37721346563659</v>
       </c>
       <c r="AG25" t="s">
         <v>278</v>
@@ -4945,12 +4935,12 @@
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B26" t="s">
         <v>271</v>
       </c>
-      <c r="C26" s="34" t="s">
+      <c r="C26" t="s">
         <v>272</v>
       </c>
       <c r="D26" t="s">
@@ -4968,8 +4958,8 @@
       <c r="H26" t="n">
         <v>0.239482940673828</v>
       </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4987,7 +4977,7 @@
         <v>-23.52</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P26" t="e">
         <v>#N/A</v>
@@ -4996,10 +4986,10 @@
         <v>#N/A</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>27.1022314251459</v>
+        <v>27.1022314251458</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="e">
         <v>#N/A</v>
@@ -5008,7 +4998,7 @@
         <v>#N/A</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W26" t="n">
         <v>0.2</v>
@@ -5017,10 +5007,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA26" t="e">
         <v>#N/A</v>
@@ -5038,7 +5028,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.29624</v>
+        <v>1.29243651141171</v>
       </c>
       <c r="AG26" t="s">
         <v>278</v>
@@ -5055,12 +5045,12 @@
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s">
         <v>271</v>
       </c>
-      <c r="C27" s="34" t="s">
+      <c r="C27" t="s">
         <v>272</v>
       </c>
       <c r="D27" t="s">
@@ -5078,8 +5068,8 @@
       <c r="H27" t="n">
         <v>0.24717936706543</v>
       </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -5097,7 +5087,7 @@
         <v>-23.2316666666667</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P27" t="e">
         <v>#N/A</v>
@@ -5106,10 +5096,10 @@
         <v>#N/A</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>27.213855602355</v>
+        <v>27.2138556023549</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" t="e">
         <v>#N/A</v>
@@ -5118,7 +5108,7 @@
         <v>#N/A</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W27" t="n">
         <v>0.2</v>
@@ -5127,10 +5117,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA27" t="e">
         <v>#N/A</v>
@@ -5148,7 +5138,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.32968</v>
+        <v>1.32582018250544</v>
       </c>
       <c r="AG27" t="s">
         <v>278</v>
@@ -5165,12 +5155,12 @@
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s">
         <v>271</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" t="s">
         <v>272</v>
       </c>
       <c r="D28" t="s">
@@ -5188,8 +5178,8 @@
       <c r="H28" t="n">
         <v>0.250065521240234</v>
       </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -5207,7 +5197,7 @@
         <v>-23.3723333333333</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P28" t="e">
         <v>#N/A</v>
@@ -5219,7 +5209,7 @@
         <v>25.7064590739005</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T28" t="e">
         <v>#N/A</v>
@@ -5228,7 +5218,7 @@
         <v>#N/A</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W28" t="n">
         <v>0.2</v>
@@ -5237,10 +5227,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA28" t="e">
         <v>#N/A</v>
@@ -5258,7 +5248,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.3288</v>
+        <v>1.32494166484508</v>
       </c>
       <c r="AG28" t="s">
         <v>278</v>
@@ -5275,12 +5265,12 @@
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s">
         <v>271</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" t="s">
         <v>272</v>
       </c>
       <c r="D29" t="s">
@@ -5298,8 +5288,8 @@
       <c r="H29" t="n">
         <v>0.257842346191406</v>
       </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -5317,7 +5307,7 @@
         <v>-23.454</v>
       </c>
       <c r="O29" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P29" t="e">
         <v>#N/A</v>
@@ -5329,7 +5319,7 @@
         <v>26.6639729856869</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T29" t="e">
         <v>#N/A</v>
@@ -5338,7 +5328,7 @@
         <v>#N/A</v>
       </c>
       <c r="V29" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W29" t="n">
         <v>0.2</v>
@@ -5347,10 +5337,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA29" t="e">
         <v>#N/A</v>
@@ -5368,7 +5358,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.37808</v>
+        <v>1.37413865382533</v>
       </c>
       <c r="AG29" t="s">
         <v>278</v>
@@ -5385,12 +5375,12 @@
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s">
         <v>271</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" t="s">
         <v>272</v>
       </c>
       <c r="D30" t="s">
@@ -5408,8 +5398,8 @@
       <c r="H30" t="n">
         <v>2.59949886</v>
       </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+      <c r="I30" t="n">
+        <v>0.006</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -5427,7 +5417,7 @@
         <v>-23.3365</v>
       </c>
       <c r="O30" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P30" t="e">
         <v>#N/A</v>
@@ -5439,7 +5429,7 @@
         <v>27.8805496137401</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="e">
         <v>#N/A</v>
@@ -5448,7 +5438,7 @@
         <v>#N/A</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W30" t="n">
         <v>0.2</v>
@@ -5457,10 +5447,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA30" t="e">
         <v>#N/A</v>
@@ -5478,7 +5468,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.331</v>
+        <v>1.32713795899599</v>
       </c>
       <c r="AG30" t="s">
         <v>278</v>
@@ -5495,12 +5485,12 @@
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" t="s">
         <v>272</v>
       </c>
       <c r="D31" t="s">
@@ -5518,8 +5508,8 @@
       <c r="H31" t="n">
         <v>2.60754347777778</v>
       </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+      <c r="I31" t="n">
+        <v>0.006</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -5537,7 +5527,7 @@
         <v>-22.248</v>
       </c>
       <c r="O31" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P31" t="e">
         <v>#N/A</v>
@@ -5549,7 +5539,7 @@
         <v>27.3004418757843</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="e">
         <v>#N/A</v>
@@ -5558,7 +5548,7 @@
         <v>#N/A</v>
       </c>
       <c r="V31" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W31" t="n">
         <v>0.2</v>
@@ -5567,28 +5557,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB31" t="e">
-        <v>#N/A</v>
+      <c r="AB31" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC31" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE31" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF31" t="e">
-        <v>#N/A</v>
+      <c r="AD31" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG31" t="s">
         <v>278</v>
@@ -5605,12 +5595,12 @@
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B32" t="s">
         <v>271</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" t="s">
         <v>272</v>
       </c>
       <c r="D32" t="s">
@@ -5628,8 +5618,8 @@
       <c r="H32" t="n">
         <v>2.617315</v>
       </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+      <c r="I32" t="n">
+        <v>0.006</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -5647,7 +5637,7 @@
         <v>-22.652</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P32" t="e">
         <v>#N/A</v>
@@ -5659,7 +5649,7 @@
         <v>27.2464952736742</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="e">
         <v>#N/A</v>
@@ -5668,7 +5658,7 @@
         <v>#N/A</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W32" t="n">
         <v>0.2</v>
@@ -5677,10 +5667,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA32" t="e">
         <v>#N/A</v>
@@ -5698,7 +5688,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.683</v>
+        <v>1.67854502314058</v>
       </c>
       <c r="AG32" t="s">
         <v>278</v>
@@ -5715,12 +5705,12 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
         <v>271</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" t="s">
         <v>272</v>
       </c>
       <c r="D33" t="s">
@@ -5738,8 +5728,8 @@
       <c r="H33" t="n">
         <v>2.62702196666667</v>
       </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+      <c r="I33" t="n">
+        <v>0.006</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -5757,7 +5747,7 @@
         <v>-22.0535</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P33" t="e">
         <v>#N/A</v>
@@ -5769,7 +5759,7 @@
         <v>27.7344512930568</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="e">
         <v>#N/A</v>
@@ -5778,7 +5768,7 @@
         <v>#N/A</v>
       </c>
       <c r="V33" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W33" t="n">
         <v>0.2</v>
@@ -5787,28 +5777,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB33" t="e">
-        <v>#N/A</v>
+      <c r="AB33" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC33" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF33" t="e">
-        <v>#N/A</v>
+      <c r="AD33" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG33" t="s">
         <v>278</v>
@@ -5825,12 +5815,12 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s">
         <v>271</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" t="s">
         <v>272</v>
       </c>
       <c r="D34" t="s">
@@ -5848,8 +5838,8 @@
       <c r="H34" t="n">
         <v>2.63361495</v>
       </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+      <c r="I34" t="n">
+        <v>0.006</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -5867,7 +5857,7 @@
         <v>-22.382</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P34" t="e">
         <v>#N/A</v>
@@ -5879,7 +5869,7 @@
         <v>27.1134057850586</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T34" t="e">
         <v>#N/A</v>
@@ -5888,7 +5878,7 @@
         <v>#N/A</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W34" t="n">
         <v>0.2</v>
@@ -5897,10 +5887,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA34" t="e">
         <v>#N/A</v>
@@ -5918,7 +5908,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.639</v>
+        <v>1.63461914012251</v>
       </c>
       <c r="AG34" t="s">
         <v>278</v>
@@ -5935,12 +5925,12 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s">
         <v>271</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" t="s">
         <v>272</v>
       </c>
       <c r="D35" t="s">
@@ -5958,8 +5948,8 @@
       <c r="H35" t="n">
         <v>2.64228622222222</v>
       </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+      <c r="I35" t="n">
+        <v>0.006</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -5977,7 +5967,7 @@
         <v>-21.816</v>
       </c>
       <c r="O35" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P35" t="e">
         <v>#N/A</v>
@@ -5989,7 +5979,7 @@
         <v>26.8419726908843</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="e">
         <v>#N/A</v>
@@ -5998,7 +5988,7 @@
         <v>#N/A</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W35" t="n">
         <v>0.2</v>
@@ -6007,28 +5997,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB35" t="e">
-        <v>#N/A</v>
+      <c r="AB35" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC35" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE35" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF35" t="e">
-        <v>#N/A</v>
+      <c r="AD35" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG35" t="s">
         <v>278</v>
@@ -6045,12 +6035,12 @@
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s">
         <v>271</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" t="s">
         <v>272</v>
       </c>
       <c r="D36" t="s">
@@ -6068,8 +6058,8 @@
       <c r="H36" t="n">
         <v>2.6506129</v>
       </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+      <c r="I36" t="n">
+        <v>0.006</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -6087,7 +6077,7 @@
         <v>-23.6425</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P36" t="e">
         <v>#N/A</v>
@@ -6099,7 +6089,7 @@
         <v>27.4502598148706</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="e">
         <v>#N/A</v>
@@ -6108,7 +6098,7 @@
         <v>#N/A</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W36" t="n">
         <v>0.2</v>
@@ -6117,10 +6107,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA36" t="e">
         <v>#N/A</v>
@@ -6138,7 +6128,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.771</v>
+        <v>1.76639678917673</v>
       </c>
       <c r="AG36" t="s">
         <v>278</v>
@@ -6155,12 +6145,12 @@
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s">
         <v>271</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" t="s">
         <v>272</v>
       </c>
       <c r="D37" t="s">
@@ -6178,8 +6168,8 @@
       <c r="H37" t="n">
         <v>2.65685448888889</v>
       </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+      <c r="I37" t="n">
+        <v>0.006</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -6197,7 +6187,7 @@
         <v>-23.315</v>
       </c>
       <c r="O37" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P37" t="e">
         <v>#N/A</v>
@@ -6209,7 +6199,7 @@
         <v>27.1962175191422</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" t="e">
         <v>#N/A</v>
@@ -6218,7 +6208,7 @@
         <v>#N/A</v>
       </c>
       <c r="V37" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W37" t="n">
         <v>0.2</v>
@@ -6227,28 +6217,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB37" t="e">
-        <v>#N/A</v>
+      <c r="AB37" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC37" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE37" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF37" t="e">
-        <v>#N/A</v>
+      <c r="AD37" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG37" t="s">
         <v>278</v>
@@ -6265,12 +6255,12 @@
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B38" t="s">
         <v>271</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" t="s">
         <v>272</v>
       </c>
       <c r="D38" t="s">
@@ -6288,8 +6278,8 @@
       <c r="H38" t="n">
         <v>2.66621956</v>
       </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+      <c r="I38" t="n">
+        <v>0.006</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -6307,7 +6297,7 @@
         <v>-22.248</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P38" t="e">
         <v>#N/A</v>
@@ -6316,10 +6306,10 @@
         <v>#N/A</v>
       </c>
       <c r="R38" s="11" t="n">
-        <v>27.7475615786215</v>
+        <v>27.7475615786214</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="e">
         <v>#N/A</v>
@@ -6328,7 +6318,7 @@
         <v>#N/A</v>
       </c>
       <c r="V38" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W38" t="n">
         <v>0.2</v>
@@ -6337,10 +6327,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA38" t="e">
         <v>#N/A</v>
@@ -6358,7 +6348,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.463</v>
+        <v>1.45891560805021</v>
       </c>
       <c r="AG38" t="s">
         <v>278</v>
@@ -6375,12 +6365,12 @@
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B39" t="s">
         <v>271</v>
       </c>
-      <c r="C39" s="34" t="s">
+      <c r="C39" t="s">
         <v>272</v>
       </c>
       <c r="D39" t="s">
@@ -6398,8 +6388,8 @@
       <c r="H39" t="n">
         <v>2.67517532</v>
       </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+      <c r="I39" t="n">
+        <v>0.006</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -6417,7 +6407,7 @@
         <v>-21.679</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P39" t="e">
         <v>#N/A</v>
@@ -6429,7 +6419,7 @@
         <v>27.7972353852215</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="e">
         <v>#N/A</v>
@@ -6438,7 +6428,7 @@
         <v>#N/A</v>
       </c>
       <c r="V39" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W39" t="n">
         <v>0.2</v>
@@ -6447,28 +6437,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB39" t="e">
-        <v>#N/A</v>
+      <c r="AB39" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC39" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE39" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF39" t="e">
-        <v>#N/A</v>
+      <c r="AD39" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG39" t="s">
         <v>278</v>
@@ -6485,12 +6475,12 @@
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s">
         <v>271</v>
       </c>
-      <c r="C40" s="34" t="s">
+      <c r="C40" t="s">
         <v>272</v>
       </c>
       <c r="D40" t="s">
@@ -6508,8 +6498,8 @@
       <c r="H40" t="n">
         <v>2.68211746666667</v>
       </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+      <c r="I40" t="n">
+        <v>0.006</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -6527,7 +6517,7 @@
         <v>-22.204</v>
       </c>
       <c r="O40" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P40" t="e">
         <v>#N/A</v>
@@ -6539,7 +6529,7 @@
         <v>27.6384981266059</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="e">
         <v>#N/A</v>
@@ -6548,7 +6538,7 @@
         <v>#N/A</v>
       </c>
       <c r="V40" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W40" t="n">
         <v>0.2</v>
@@ -6557,10 +6547,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA40" t="e">
         <v>#N/A</v>
@@ -6578,7 +6568,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.595</v>
+        <v>1.59069325710443</v>
       </c>
       <c r="AG40" t="s">
         <v>278</v>
@@ -6595,12 +6585,12 @@
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s">
         <v>271</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" t="s">
         <v>272</v>
       </c>
       <c r="D41" t="s">
@@ -6618,8 +6608,8 @@
       <c r="H41" t="n">
         <v>2.6882203</v>
       </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+      <c r="I41" t="n">
+        <v>0.006</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -6637,7 +6627,7 @@
         <v>-24.137</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P41" t="e">
         <v>#N/A</v>
@@ -6649,7 +6639,7 @@
         <v>27.3273323436146</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T41" t="e">
         <v>#N/A</v>
@@ -6658,7 +6648,7 @@
         <v>#N/A</v>
       </c>
       <c r="V41" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W41" t="n">
         <v>0.2</v>
@@ -6667,28 +6657,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB41" t="e">
-        <v>#N/A</v>
+      <c r="AB41" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC41" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE41" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF41" t="e">
-        <v>#N/A</v>
+      <c r="AD41" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG41" t="s">
         <v>278</v>
@@ -6705,12 +6695,12 @@
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="34" t="s">
+      <c r="C42" t="s">
         <v>272</v>
       </c>
       <c r="D42" t="s">
@@ -6728,8 +6718,8 @@
       <c r="H42" t="n">
         <v>2.6934895</v>
       </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+      <c r="I42" t="n">
+        <v>0.006</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -6747,7 +6737,7 @@
         <v>-24.061</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P42" t="e">
         <v>#N/A</v>
@@ -6759,7 +6749,7 @@
         <v>28.1361533823898</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" t="e">
         <v>#N/A</v>
@@ -6768,7 +6758,7 @@
         <v>#N/A</v>
       </c>
       <c r="V42" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W42" t="n">
         <v>0.2</v>
@@ -6777,10 +6767,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA42" t="e">
         <v>#N/A</v>
@@ -6798,7 +6788,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.639</v>
+        <v>1.63461914012251</v>
       </c>
       <c r="AG42" t="s">
         <v>278</v>
@@ -6815,12 +6805,12 @@
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="34" t="s">
+      <c r="C43" t="s">
         <v>272</v>
       </c>
       <c r="D43" t="s">
@@ -6838,8 +6828,8 @@
       <c r="H43" t="n">
         <v>2.69876056666667</v>
       </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+      <c r="I43" t="n">
+        <v>0.006</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -6857,7 +6847,7 @@
         <v>-23.7145</v>
       </c>
       <c r="O43" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P43" t="e">
         <v>#N/A</v>
@@ -6869,7 +6859,7 @@
         <v>27.6208007501454</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T43" t="e">
         <v>#N/A</v>
@@ -6878,7 +6868,7 @@
         <v>#N/A</v>
       </c>
       <c r="V43" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W43" t="n">
         <v>0.2</v>
@@ -6887,28 +6877,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB43" t="e">
-        <v>#N/A</v>
+      <c r="AB43" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC43" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE43" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF43" t="e">
-        <v>#N/A</v>
+      <c r="AD43" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG43" t="s">
         <v>278</v>
@@ -6925,12 +6915,12 @@
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s">
         <v>271</v>
       </c>
-      <c r="C44" s="34" t="s">
+      <c r="C44" t="s">
         <v>272</v>
       </c>
       <c r="D44" t="s">
@@ -6948,8 +6938,8 @@
       <c r="H44" t="n">
         <v>2.70486522222222</v>
       </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+      <c r="I44" t="n">
+        <v>0.006</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -6967,7 +6957,7 @@
         <v>-23.23275</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P44" t="e">
         <v>#N/A</v>
@@ -6979,7 +6969,7 @@
         <v>27.056</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T44" t="e">
         <v>#N/A</v>
@@ -6988,7 +6978,7 @@
         <v>#N/A</v>
       </c>
       <c r="V44" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W44" t="n">
         <v>0.2</v>
@@ -6997,10 +6987,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA44" t="e">
         <v>#N/A</v>
@@ -7018,7 +7008,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.771</v>
+        <v>1.76639678917673</v>
       </c>
       <c r="AG44" t="s">
         <v>278</v>
@@ -7035,12 +7025,12 @@
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="34" t="s">
+      <c r="C45" t="s">
         <v>272</v>
       </c>
       <c r="D45" t="s">
@@ -7058,8 +7048,8 @@
       <c r="H45" t="n">
         <v>2.70903086666667</v>
       </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+      <c r="I45" t="n">
+        <v>0.006</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -7077,7 +7067,7 @@
         <v>-22.2355</v>
       </c>
       <c r="O45" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P45" t="e">
         <v>#N/A</v>
@@ -7089,7 +7079,7 @@
         <v>26.677354291895</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" t="e">
         <v>#N/A</v>
@@ -7098,7 +7088,7 @@
         <v>#N/A</v>
       </c>
       <c r="V45" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W45" t="n">
         <v>0.2</v>
@@ -7107,28 +7097,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB45" t="e">
-        <v>#N/A</v>
+      <c r="AB45" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE45" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF45" t="e">
-        <v>#N/A</v>
+      <c r="AD45" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG45" t="s">
         <v>278</v>
@@ -7145,12 +7135,12 @@
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B46" t="s">
         <v>271</v>
       </c>
-      <c r="C46" s="34" t="s">
+      <c r="C46" t="s">
         <v>272</v>
       </c>
       <c r="D46" t="s">
@@ -7168,8 +7158,8 @@
       <c r="H46" t="n">
         <v>2.714304</v>
       </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+      <c r="I46" t="n">
+        <v>0.006</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -7187,7 +7177,7 @@
         <v>-23.5433333333333</v>
       </c>
       <c r="O46" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P46" t="e">
         <v>#N/A</v>
@@ -7199,7 +7189,7 @@
         <v>26.0797168839379</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T46" t="e">
         <v>#N/A</v>
@@ -7208,7 +7198,7 @@
         <v>#N/A</v>
       </c>
       <c r="V46" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W46" t="n">
         <v>0.2</v>
@@ -7217,28 +7207,28 @@
         <v>#N/A</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AB46" t="e">
-        <v>#N/A</v>
+      <c r="AB46" t="n">
+        <v>5.661324</v>
       </c>
       <c r="AC46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="AD46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE46" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF46" t="e">
-        <v>#N/A</v>
+      <c r="AD46" t="n">
+        <v>1.96666666666667</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>9.35598133333333</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.75970332407639</v>
       </c>
       <c r="AG46" t="s">
         <v>278</v>
@@ -7255,12 +7245,12 @@
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B47" t="s">
         <v>271</v>
       </c>
-      <c r="C47" s="34" t="s">
+      <c r="C47" t="s">
         <v>272</v>
       </c>
       <c r="D47" t="s">
@@ -7278,8 +7268,8 @@
       <c r="H47" t="n">
         <v>2.74185501</v>
       </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+      <c r="I47" t="n">
+        <v>0.006</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -7297,7 +7287,7 @@
         <v>-22.8785</v>
       </c>
       <c r="O47" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P47" t="e">
         <v>#N/A</v>
@@ -7309,7 +7299,7 @@
         <v>28.3352020052287</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T47" t="e">
         <v>#N/A</v>
@@ -7318,7 +7308,7 @@
         <v>#N/A</v>
       </c>
       <c r="V47" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W47" t="n">
         <v>0.2</v>
@@ -7327,10 +7317,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA47" t="e">
         <v>#N/A</v>
@@ -7348,7 +7338,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.771</v>
+        <v>1.76639678917673</v>
       </c>
       <c r="AG47" t="s">
         <v>278</v>
@@ -7365,12 +7355,12 @@
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B48" t="s">
         <v>271</v>
       </c>
-      <c r="C48" s="34" t="s">
+      <c r="C48" t="s">
         <v>272</v>
       </c>
       <c r="D48" t="s">
@@ -7388,8 +7378,8 @@
       <c r="H48" t="n">
         <v>2.75226265</v>
       </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+      <c r="I48" t="n">
+        <v>0.006</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -7407,7 +7397,7 @@
         <v>-22.6885</v>
       </c>
       <c r="O48" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P48" t="e">
         <v>#N/A</v>
@@ -7419,7 +7409,7 @@
         <v>27.8409387527755</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T48" t="e">
         <v>#N/A</v>
@@ -7428,7 +7418,7 @@
         <v>#N/A</v>
       </c>
       <c r="V48" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W48" t="n">
         <v>0.2</v>
@@ -7437,10 +7427,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA48" t="e">
         <v>#N/A</v>
@@ -7458,7 +7448,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.771</v>
+        <v>1.76639678917673</v>
       </c>
       <c r="AG48" t="s">
         <v>278</v>
@@ -7475,12 +7465,12 @@
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B49" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="34" t="s">
+      <c r="C49" t="s">
         <v>272</v>
       </c>
       <c r="D49" t="s">
@@ -7498,8 +7488,8 @@
       <c r="H49" t="n">
         <v>2.76613998947368</v>
       </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+      <c r="I49" t="n">
+        <v>0.006</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -7517,7 +7507,7 @@
         <v>-22.4595</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P49" t="e">
         <v>#N/A</v>
@@ -7529,7 +7519,7 @@
         <v>27.7420835948129</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T49" t="e">
         <v>#N/A</v>
@@ -7538,7 +7528,7 @@
         <v>#N/A</v>
       </c>
       <c r="V49" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W49" t="n">
         <v>0.2</v>
@@ -7547,10 +7537,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA49" t="e">
         <v>#N/A</v>
@@ -7568,7 +7558,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.727</v>
+        <v>1.72247090615866</v>
       </c>
       <c r="AG49" t="s">
         <v>278</v>
@@ -7585,12 +7575,12 @@
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B50" t="s">
         <v>271</v>
       </c>
-      <c r="C50" s="34" t="s">
+      <c r="C50" t="s">
         <v>272</v>
       </c>
       <c r="D50" t="s">
@@ -7608,8 +7598,8 @@
       <c r="H50" t="n">
         <v>2.78155956666667</v>
       </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+      <c r="I50" t="n">
+        <v>0.006</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -7627,7 +7617,7 @@
         <v>-23.6375</v>
       </c>
       <c r="O50" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P50" t="e">
         <v>#N/A</v>
@@ -7639,7 +7629,7 @@
         <v>27.5928580280126</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="e">
         <v>#N/A</v>
@@ -7648,7 +7638,7 @@
         <v>#N/A</v>
       </c>
       <c r="V50" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W50" t="n">
         <v>0.2</v>
@@ -7657,10 +7647,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA50" t="e">
         <v>#N/A</v>
@@ -7678,7 +7668,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.639</v>
+        <v>1.63461914012251</v>
       </c>
       <c r="AG50" t="s">
         <v>278</v>
@@ -7695,12 +7685,12 @@
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B51" t="s">
         <v>271</v>
       </c>
-      <c r="C51" s="34" t="s">
+      <c r="C51" t="s">
         <v>272</v>
       </c>
       <c r="D51" t="s">
@@ -7718,8 +7708,8 @@
       <c r="H51" t="n">
         <v>2.78960594210526</v>
       </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+      <c r="I51" t="n">
+        <v>0.006</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -7737,7 +7727,7 @@
         <v>-22.6575</v>
       </c>
       <c r="O51" t="n">
-        <v>0.6</v>
+        <v>0.424264068711928</v>
       </c>
       <c r="P51" t="e">
         <v>#N/A</v>
@@ -7749,7 +7739,7 @@
         <v>27.6038534047154</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" t="e">
         <v>#N/A</v>
@@ -7758,7 +7748,7 @@
         <v>#N/A</v>
       </c>
       <c r="V51" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W51" t="n">
         <v>0.2</v>
@@ -7767,10 +7757,10 @@
         <v>#N/A</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="AA51" t="e">
         <v>#N/A</v>
@@ -7788,7 +7778,7 @@
         <v>#N/A</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.683</v>
+        <v>1.67854502314058</v>
       </c>
       <c r="AG51" t="s">
         <v>278</v>
@@ -8029,55 +8019,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
